--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104603_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104603_W17.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6786</v>
+        <v>5.773</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5518</v>
+        <v>3.9469</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1267</v>
+        <v>1.826</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5569</v>
+        <v>3.5552</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2654</v>
+        <v>5.2591</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.7086</v>
+        <v>-1.7039</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7262</v>
+        <v>4.6952</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4331</v>
+        <v>4.4126</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2931</v>
+        <v>0.2826</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.1693</v>
+        <v>-1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8324</v>
+        <v>0.8465</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3566</v>
+        <v>-0.2587</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0253</v>
+        <v>-0.581</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6687</v>
+        <v>0.3223</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.834</v>
+        <v>3.3879</v>
       </c>
       <c r="E3" t="n">
-        <v>3.985</v>
+        <v>4.7378</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.151</v>
+        <v>-1.3499</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3667</v>
+        <v>-1.3697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.723</v>
+        <v>0.7156</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0897</v>
+        <v>-2.0853</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2357</v>
+        <v>2.1925</v>
       </c>
       <c r="K3" t="n">
-        <v>1.087</v>
+        <v>1.0612</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1487</v>
+        <v>1.1313</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6024</v>
+        <v>-3.5623</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.2384</v>
+        <v>-3.2166</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0773</v>
+        <v>-0.5108</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5818</v>
+        <v>-0.7623</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5044</v>
+        <v>0.2515</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6921</v>
+        <v>4.6734</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8735000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.036</v>
+        <v>0.1941</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8375</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.5109</v>
+        <v>0.2284</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6614</v>
+        <v>-1.1404</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1723</v>
+        <v>1.3688</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2634</v>
+        <v>1.7159</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0022</v>
+        <v>-0.8381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2612</v>
+        <v>2.554</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7743</v>
+        <v>-1.4876</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6592</v>
+        <v>-0.3023</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4335</v>
+        <v>-1.1852</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1757</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8892</v>
+        <v>0.0476</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1996</v>
+        <v>-0.156</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6895</v>
+        <v>0.2036</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2534</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.857</v>
+        <v>0.0052</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1589</v>
+        <v>-0.5677</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6981000000000001</v>
+        <v>0.573</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4289</v>
+        <v>-1.5267</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0028</v>
+        <v>0.6279</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4318</v>
+        <v>-2.1547</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0346</v>
+        <v>0.2145</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0346</v>
+        <v>-0.0462</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.2607</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4636</v>
+        <v>-1.7412</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0318</v>
+        <v>0.6741</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4318</v>
+        <v>-2.4154</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.1868</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5039</v>
+        <v>0.028</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5777</v>
+        <v>-0.3466</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0738</v>
+        <v>0.3746</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7712</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1217</v>
+        <v>-1.0193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6449</v>
+        <v>-0.838</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4767</v>
+        <v>-0.1813</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2284</v>
+        <v>-2.0459</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1443</v>
+        <v>0.5311</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3727</v>
+        <v>-2.577</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7413</v>
+        <v>-0.5568</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8280999999999999</v>
+        <v>0.948</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5694</v>
+        <v>-1.5048</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.513</v>
+        <v>-1.4891</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3162</v>
+        <v>-0.4169</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1967</v>
+        <v>-1.0722</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1647</v>
+        <v>-0.2497</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0253</v>
+        <v>-0.2812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1394</v>
+        <v>0.0316</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.132</v>
+        <v>-1.1971</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.084</v>
+        <v>-0.6327</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.048</v>
+        <v>-0.5643</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.051</v>
+        <v>-0.4233</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5266</v>
+        <v>0.0056</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.5776</v>
+        <v>-0.4289</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5457</v>
+        <v>0.0345</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9524</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4981</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5053</v>
+        <v>-0.4578</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4258</v>
+        <v>-0.0289</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0795</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3493</v>
+        <v>0.1579</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5383</v>
+        <v>0.1067</v>
       </c>
       <c r="U7" t="n">
-        <v>0.189</v>
+        <v>0.0512</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6783</v>
+        <v>-1.3098</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.5041</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8824</v>
+        <v>-0.8058</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1387</v>
+        <v>-0.1302</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9408</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="J8" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="K8" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7967</v>
+        <v>-0.7852</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2032</v>
+        <v>0.165</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>0.0278</v>
       </c>
       <c r="U8" t="n">
-        <v>0.075</v>
+        <v>0.1372</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.975</v>
+        <v>-1.6167</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1649</v>
+        <v>-0.912</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8101</v>
+        <v>-0.7047</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3733</v>
+        <v>-2.3686</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2698</v>
+        <v>-1.2695</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1035</v>
+        <v>-1.0991</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.6635</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7135</v>
+        <v>-1.7052</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3729</v>
+        <v>-0.0221</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6538</v>
+        <v>-2.2958</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7081</v>
+        <v>-0.7451</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9457</v>
+        <v>-1.5507</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5109</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9552</v>
+        <v>2.9526</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4443</v>
+        <v>-2.446</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8852</v>
+        <v>1.8478</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6424</v>
+        <v>2.6233</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3743</v>
+        <v>-1.3412</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6871</v>
+        <v>-1.6706</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.711</v>
+        <v>-0.3472</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6049</v>
+        <v>-0.5835</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1062</v>
+        <v>0.2363</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5978</v>
+        <v>-3.7105</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4336</v>
+        <v>-2.6674</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1642</v>
+        <v>-1.0431</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.854</v>
+        <v>-3.8464</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8687</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9853</v>
+        <v>-2.9789</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7411</v>
+        <v>-1.7588</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9147</v>
+        <v>-0.9243</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8264</v>
+        <v>-0.8345</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.113</v>
+        <v>-2.0876</v>
       </c>
       <c r="N11" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6512</v>
+        <v>-0.7747000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4657</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1854</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.629499999999998</v>
+        <v>-1.886000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5824999999999996</v>
+        <v>2.0118</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.212</v>
+        <v>-3.8979</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.427300000000001</v>
+        <v>-7.4206</v>
       </c>
       <c r="H12" t="n">
-        <v>7.792399999999999</v>
+        <v>7.756600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-15.2199</v>
+        <v>-15.1772</v>
       </c>
       <c r="J12" t="n">
-        <v>8.597799999999999</v>
+        <v>8.376300000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>7.3325</v>
+        <v>7.188100000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2653</v>
+        <v>1.1884</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.0254</v>
+        <v>-15.7972</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4601999999999999</v>
+        <v>0.5685000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-16.4853</v>
+        <v>-16.3656</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R12" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.4931</v>
+        <v>-1.7647</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.0204</v>
+        <v>-3.278</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5271</v>
+        <v>1.5135</v>
       </c>
       <c r="V12" t="n">
-        <v>3.888500000000001</v>
+        <v>3.8846</v>
       </c>
       <c r="W12" t="n">
-        <v>9.4809</v>
+        <v>9.433199999999998</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.5922</v>
+        <v>-5.5486</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4418</v>
+        <v>5.1877</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6271</v>
+        <v>4.2177</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8147</v>
+        <v>0.9701</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3484</v>
+        <v>5.3296</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.8325</v>
+        <v>-1.8378</v>
       </c>
       <c r="I13" t="n">
-        <v>7.1808</v>
+        <v>7.1674</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6723</v>
+        <v>5.6303</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.154</v>
+        <v>-1.1763</v>
       </c>
       <c r="L13" t="n">
-        <v>6.8263</v>
+        <v>6.8067</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3239</v>
+        <v>-0.3007</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5205</v>
+        <v>0.2938</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0302</v>
+        <v>-0.3836</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5507</v>
+        <v>0.6774</v>
       </c>
       <c r="V13" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1107</v>
+        <v>4.2133</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3625</v>
+        <v>2.628</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7482</v>
+        <v>1.5853</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4182</v>
+        <v>4.4138</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3333</v>
+        <v>3.3263</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0849</v>
+        <v>1.0875</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9272</v>
+        <v>3.9108</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2555</v>
+        <v>3.2405</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M14" t="n">
-        <v>0.491</v>
+        <v>0.503</v>
       </c>
       <c r="N14" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0554</v>
+        <v>1.1637</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3822</v>
+        <v>0.678</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6732</v>
+        <v>0.4857</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0965</v>
+        <v>-0.0863</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9708</v>
+        <v>3.1474</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1656</v>
+        <v>2.2626</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8052</v>
+        <v>0.8848</v>
       </c>
       <c r="G15" t="n">
-        <v>2.151</v>
+        <v>2.1508</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1514</v>
+        <v>1.1544</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9964</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5368</v>
+        <v>2.5229</v>
       </c>
       <c r="K15" t="n">
-        <v>1.42</v>
+        <v>1.4134</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3858</v>
+        <v>-0.372</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.046</v>
+        <v>0.1348</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3297</v>
+        <v>-0.2115</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2837</v>
+        <v>0.3463</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7955</v>
+        <v>1.8817</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1844</v>
+        <v>1.6904</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6111</v>
+        <v>0.1913</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.3796</v>
+        <v>-1.3806</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3881</v>
+        <v>-0.3932</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9915</v>
+        <v>-0.9874000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2243</v>
+        <v>0.2099</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0377</v>
+        <v>0.0237</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6039</v>
+        <v>-1.5906</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2412</v>
+        <v>0.3322</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1603</v>
+        <v>-0.3115</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0809</v>
+        <v>0.6437</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.3547</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1337</v>
+        <v>1.8692</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5819</v>
+        <v>-1.5145</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9283</v>
+        <v>0.9402</v>
       </c>
       <c r="H17" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8823</v>
+        <v>0.8834</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2485</v>
+        <v>3.2331</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3853</v>
+        <v>1.3789</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8631</v>
+        <v>1.8542</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.3202</v>
+        <v>-2.2929</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3702</v>
+        <v>0.1672</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0998</v>
+        <v>-0.3349</v>
       </c>
       <c r="U17" t="n">
-        <v>0.47</v>
+        <v>0.5021</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3407</v>
+        <v>-0.3037</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6516</v>
+        <v>-0.9364</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9923</v>
+        <v>0.6327</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0214</v>
+        <v>-0.9693000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5514</v>
+        <v>-0.2362</v>
       </c>
       <c r="I18" t="n">
-        <v>1.53</v>
+        <v>-0.7331</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7233000000000001</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3534</v>
+        <v>0.0517</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0768</v>
+        <v>-0.8345</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7447</v>
+        <v>-0.1865</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.198</v>
+        <v>-0.2879</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>0.1014</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2536</v>
+        <v>-0.0871</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0302</v>
+        <v>-0.1535</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2838</v>
+        <v>0.0664</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7997</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.8924</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.07</v>
+        <v>-0.3938</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4005</v>
+        <v>0.8657</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3305</v>
+        <v>-1.2595</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9761</v>
+        <v>-0.0106</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2484</v>
+        <v>-1.5373</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7277</v>
+        <v>1.5267</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7744</v>
+        <v>0.7058</v>
       </c>
       <c r="K19" t="n">
-        <v>0.052</v>
+        <v>-0.3587</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8264</v>
+        <v>1.0645</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2017</v>
+        <v>-0.7164</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3003</v>
+        <v>-1.1786</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.4622</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8405</v>
+        <v>1.1812</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6261</v>
+        <v>0.2086</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2144</v>
+        <v>0.9726</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-1.792</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>O. LIVINGSTON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2975</v>
+        <v>-0.6108</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0132</v>
+        <v>-1.1084</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2842</v>
+        <v>0.4976</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.7117</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1443</v>
+        <v>-1.9245</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6953</v>
+        <v>2.6361</v>
       </c>
       <c r="J20" t="n">
-        <v>1.499</v>
+        <v>1.9427</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2149</v>
+        <v>-0.976</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7139</v>
+        <v>2.9187</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.948</v>
+        <v>-1.231</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9294</v>
+        <v>-0.9485</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0186</v>
+        <v>-0.2826</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6979</v>
+        <v>0.4319</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7561</v>
+        <v>-0.3163</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9418</v>
+        <v>0.7482</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1853</v>
+        <v>-0.6162</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. LIVINGSTON</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7117</v>
+        <v>-1.0695</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7701</v>
+        <v>-2.6138</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0584</v>
+        <v>1.5444</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7189</v>
+        <v>-1.5569</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9278</v>
+        <v>-1.2154</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6468</v>
+        <v>-0.3415</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9733</v>
+        <v>-1.4446</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9666</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>2.9399</v>
+        <v>-0.5891999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2543</v>
+        <v>-0.1124</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.3601</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2931</v>
+        <v>0.2477</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6859</v>
+        <v>-0.1743</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0253</v>
+        <v>-0.3953</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3393</v>
+        <v>0.2211</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6105</v>
+        <v>-0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.4498</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1438</v>
+        <v>-2.1229</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0552</v>
+        <v>-0.7412</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9114</v>
+        <v>-1.3817</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.5585</v>
+        <v>0.5532</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2252</v>
+        <v>-1.1404</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3333</v>
+        <v>1.6936</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.416</v>
+        <v>1.4844</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.8454</v>
+        <v>-0.2208</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5706</v>
+        <v>1.7052</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1425</v>
+        <v>-0.9312</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3798</v>
+        <v>-0.9196</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2373</v>
+        <v>-0.0116</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5878</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q22" t="n">
+        <v>-2.2763</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.8686</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8179</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-2.1789</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.5878</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-1.2412</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-0.868</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.3732</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-0.7712</v>
-      </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6775</v>
+        <v>-5.8658</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6738</v>
+        <v>-4.2359</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0037</v>
+        <v>-1.6299</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7528</v>
+        <v>-2.7611</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.0056</v>
+        <v>-4.0092</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2528</v>
+        <v>1.2481</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.5889</v>
+        <v>-1.6155</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.0762</v>
+        <v>-3.0896</v>
       </c>
       <c r="L23" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.832</v>
+        <v>-0.0152</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8166</v>
+        <v>-0.3441</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0154</v>
+        <v>0.3289</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.629499999999998</v>
+        <v>4.4183</v>
       </c>
       <c r="E24" t="n">
-        <v>4.212100000000003</v>
+        <v>3.897900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5826</v>
+        <v>0.5206000000000002</v>
       </c>
       <c r="G24" t="n">
-        <v>7.427299999999999</v>
+        <v>7.420800000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-7.7926</v>
+        <v>-7.756500000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>15.2199</v>
+        <v>15.1772</v>
       </c>
       <c r="J24" t="n">
-        <v>16.0254</v>
+        <v>15.797</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.46</v>
+        <v>-0.5684999999999998</v>
       </c>
       <c r="L24" t="n">
-        <v>16.4854</v>
+        <v>16.3656</v>
       </c>
       <c r="M24" t="n">
-        <v>-8.597899999999999</v>
+        <v>-8.3764</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.332400000000001</v>
+        <v>-7.188099999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2654</v>
+        <v>-1.1882</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8782</v>
+        <v>-15.9342</v>
       </c>
       <c r="R24" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4932</v>
+        <v>4.2968</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5273</v>
+        <v>-1.5134</v>
       </c>
       <c r="U24" t="n">
-        <v>5.0204</v>
+        <v>5.8103</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.888399999999999</v>
+        <v>-3.8845</v>
       </c>
       <c r="W24" t="n">
-        <v>5.5923</v>
+        <v>5.5486</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.480599999999999</v>
+        <v>-9.433100000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104603_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104603_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.5486</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.0863</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104603_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.433100000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
